--- a/course-design-2/outputs/tables/ch3/13_company_text_semantic_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/13_company_text_semantic_audit.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_公司简介快照总体统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_同时间简介候选数分布" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_AMBIGUOUS公司时间点" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_主候选支持率分布" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_正式公司简介版本统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_重构前后版本数量对比" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_重构前后事件数量对比" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_跨歧义快照变化事件" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_公司简介语义距离" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公司简介变化候选类型" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_公司简介语义变化事件" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_公司实体版本明细" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_语义距离分位数" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_新增业务关键词统计" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="01_公司简介快照总体统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_同时间简介候选数分布" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_AMBIGUOUS公司时间点" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_主候选支持率分布" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_正式公司简介版本统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_重构前后版本数量对比" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_重构前后事件数量对比" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_跨歧义快照变化事件" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_公司简介语义距离" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_公司简介变化候选类型" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_公司简介语义变化事件" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_公司实体版本明细" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_语义距离分位数" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_新增业务关键词统计" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29922,7 +29922,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -29943,7 +29943,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -29964,7 +29964,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -30616,20 +30616,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4887</v>
+        <v>3899</v>
       </c>
       <c r="C2" t="n">
         <v>3899</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-988</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.202169</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -30647,17 +30647,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4452</v>
+        <v>4377</v>
       </c>
       <c r="C3" t="n">
         <v>3664</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-788</v>
+        <v>-713</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.176999</v>
+        <v>-0.162897</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -30739,20 +30739,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="C2" t="n">
         <v>235</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.45977</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -30770,20 +30770,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.636364</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>

--- a/course-design-2/outputs/tables/ch3/13_company_text_semantic_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/13_company_text_semantic_audit.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_公司简介快照总体统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_同时间简介候选数分布" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_AMBIGUOUS公司时间点" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_主候选支持率分布" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_正式公司简介版本统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_重构前后版本数量对比" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_重构前后事件数量对比" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_跨歧义快照变化事件" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_公司简介语义距离" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_公司简介变化候选类型" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_公司简介语义变化事件" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_公司实体版本明细" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_语义距离分位数" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_新增业务关键词统计" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_公司简介快照总体统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_同时间简介候选数分布" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_AMBIGUOUS公司时间点" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_主候选支持率分布" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_正式公司简介版本统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_重构前后版本数量对比" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_重构前后事件数量对比" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_跨歧义快照变化事件" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_公司简介语义距离" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公司简介变化候选类型" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_公司简介语义变化事件" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_公司实体版本明细" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_语义距离分位数" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_新增业务关键词统计" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29922,7 +29922,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -29943,7 +29943,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -29964,7 +29964,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -30616,20 +30616,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3899</v>
+        <v>4887</v>
       </c>
       <c r="C2" t="n">
         <v>3899</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-988</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.202169</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -30647,17 +30647,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4377</v>
+        <v>4452</v>
       </c>
       <c r="C3" t="n">
         <v>3664</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-713</v>
+        <v>-788</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.162897</v>
+        <v>-0.176999</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -30739,20 +30739,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>235</v>
+        <v>435</v>
       </c>
       <c r="C2" t="n">
         <v>235</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.45977</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -30770,20 +30770,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.636364</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
